--- a/ksoft/docs/records/Operation_Code_Records.xlsx
+++ b/ksoft/docs/records/Operation_Code_Records.xlsx
@@ -11668,13 +11668,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{ED6C7D02-3237-49A8-9C1B-E798AC98320D}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5CB2B831-2DB6-4D81-B408-FEA844F72FF8}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C4066F68-E225-4DED-9457-847C8EA30C5E}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EDEA7229-AE15-489D-9E6B-14D7BCC9CEFA}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FDBCDE1D-68D6-4F24-90B6-BA1A9E5F345A}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{09863061-C498-4336-966E-0879764DEFE4}"/>
 </file>
--- a/ksoft/docs/records/Operation_Code_Records.xlsx
+++ b/ksoft/docs/records/Operation_Code_Records.xlsx
@@ -11668,13 +11668,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5CB2B831-2DB6-4D81-B408-FEA844F72FF8}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{ED6C7D02-3237-49A8-9C1B-E798AC98320D}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EDEA7229-AE15-489D-9E6B-14D7BCC9CEFA}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C4066F68-E225-4DED-9457-847C8EA30C5E}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{09863061-C498-4336-966E-0879764DEFE4}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FDBCDE1D-68D6-4F24-90B6-BA1A9E5F345A}"/>
 </file>